--- a/examples/demo_annotated.xlsx
+++ b/examples/demo_annotated.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Budget" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Budget" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,179 +140,18 @@
     <author>Spreadsheet Auditor</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data column
-Fix: Confirm whether Budget!A2 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data column
-Fix: Confirm whether Budget!A3 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
-    <comment ref="B4" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data row
-Fix: Confirm whether Budget!B1 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
-    <comment ref="C4" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data row
-Fix: Confirm whether Budget!C1 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data row
-Fix: Confirm whether Budget!D1 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data column
-Fix: Confirm whether Budget!A5 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
     <comment ref="B6" authorId="0" shapeId="0">
       <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="C6" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
+        <t>High TOTAL_MISMATCH
+Total double-counts a cell inside its own range
+Fix: Remove the duplicated term or shrink the range so each component is counted once.</t>
       </text>
     </comment>
     <comment ref="E6" authorId="0" shapeId="0">
       <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="C7" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="D7" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="E7" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data column
-Fix: Confirm whether Budget!A7 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="C8" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="D8" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="E8" authorId="0" shapeId="0">
-      <text>
-        <t>Critical RANGE_EXCLUSION
-Aggregation range appears to exclude adjacent data column
-Fix: Confirm whether Budget!A8 belongs in the aggregate, then extend the range if appropriate.</t>
-      </text>
-    </comment>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="C9" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="D9" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
+        <t>High FORMULA_DRIFT
+Formula breaks neighboring pattern
+Fix: Compare this formula to adjacent formulas and restore the intended relative references.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -322,74 +161,18 @@
 Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="B11" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="C11" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="D11" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="E11" authorId="0" shapeId="0">
-      <text>
-        <t>High RANGE_INCLUDES_SUBTOTAL
-Aggregation range appears to include subtotal or total row
-Fix: Review the aggregate range and exclude subtotal/total rows unless intentionally double-counting.</t>
-      </text>
-    </comment>
-    <comment ref="B12" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="D12" authorId="0" shapeId="0">
-      <text>
-        <t>High HARDCODE_IN_FORMULA_BLOCK
-Hardcoded value inside formula block
-Fix: Confirm whether this is an intentional plug. If not, restore the formula pattern.</t>
-      </text>
-    </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
-      <text>
-        <t>Medium HIDDEN_STRUCTURE_IN_TOTAL
-Aggregate includes hidden structure
-Fix: Confirm hidden inputs are intentional and disclosed in visible workbook documentation.</t>
-      </text>
-    </comment>
-    <comment ref="E13" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0">
       <text>
         <t>High FORMULA_DRIFT
 Formula breaks neighboring pattern
 Fix: Compare this formula to adjacent formulas and restore the intended relative references.</t>
+      </text>
+    </comment>
+    <comment ref="B13" authorId="0" shapeId="0">
+      <text>
+        <t>Medium HIDDEN_STRUCTURE_IN_TOTAL
+Formula inputs include hidden structure
+Fix: Confirm hidden inputs are intentional and disclosed in visible workbook documentation.</t>
       </text>
     </comment>
     <comment ref="B14" authorId="0" shapeId="0">
@@ -402,8 +185,8 @@
     <comment ref="A17" authorId="0" shapeId="0">
       <text>
         <t>Medium DUPLICATE_KEY
-Duplicate normalized key in first column
-Fix: Confirm duplicate labels are intentional, especially if lookup formulas depend on this column.</t>
+Duplicate key in lookup range
+Fix: Make the keys unique or confirm the lookup is meant to return the first match.</t>
       </text>
     </comment>
     <comment ref="A18" authorId="0" shapeId="0">
@@ -833,15 +616,15 @@
         </is>
       </c>
       <c r="B6">
-        <f>SUM(B2:B5)+B5</f>
+        <f>SUM(B4:B5)+B5</f>
         <v/>
       </c>
       <c r="C6">
-        <f>SUM(C2:C5)</f>
+        <f>SUM(C4:C5)</f>
         <v/>
       </c>
       <c r="D6">
-        <f>SUM(D2:D5)</f>
+        <f>SUM(D4:D5)</f>
         <v/>
       </c>
       <c r="E6">
@@ -915,7 +698,7 @@
         </is>
       </c>
       <c r="B10">
-        <f>SUM(B7:B9)</f>
+        <f>SUM(B7:B8)</f>
         <v/>
       </c>
       <c r="C10">
@@ -934,19 +717,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Grand total</t>
+          <t>Net</t>
         </is>
       </c>
       <c r="B11">
-        <f>SUM(B2:B8)</f>
+        <f>B6-B10</f>
         <v/>
       </c>
       <c r="C11">
-        <f>SUM(C2:C9)</f>
+        <f>C6-C10</f>
         <v/>
       </c>
       <c r="D11">
-        <f>SUM(D2:D9)</f>
+        <f>D6-D10</f>
         <v/>
       </c>
       <c r="E11">
@@ -1080,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1099,6 +882,38 @@
         <v/>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Owner lookup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
+      <c r="C2">
+        <f>VLOOKUP(B2,Budget!A17:B19,2,FALSE)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Bonus accrual</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="C3">
+        <f>SUM(Budget!B20:B20)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/examples/demo_annotated.xlsx
+++ b/examples/demo_annotated.xlsx
@@ -142,16 +142,22 @@
   <commentList>
     <comment ref="B6" authorId="0" shapeId="0">
       <text>
-        <t>High TOTAL_MISMATCH
+        <t>High FORMULA_DRIFT
+Formula breaks neighboring pattern
+Fix: If this cell is the same kind of line as its neighbors, restore their pattern. A total, net or summary line differs by design: compare it with the other totals instead.
+High TOTAL_MISMATCH
 Total double-counts a cell inside its own range
 Fix: Remove the duplicated term or shrink the range so each component is counted once.</t>
       </text>
     </comment>
     <comment ref="E6" authorId="0" shapeId="0">
       <text>
-        <t>High FORMULA_DRIFT
+        <t>Critical CROSS_FOOT_FAILURE
+Row totals and column totals disagree
+Fix: Reconcile the totals row and totals column; one of the contributing aggregates is likely wrong.
+High FORMULA_DRIFT
 Formula breaks neighboring pattern
-Fix: Compare this formula to adjacent formulas and restore the intended relative references.</t>
+Fix: If this cell is the same kind of line as its neighbors, restore their pattern. A total, net or summary line differs by design: compare it with the other totals instead.</t>
       </text>
     </comment>
     <comment ref="E9" authorId="0" shapeId="0">
@@ -163,9 +169,12 @@
     </comment>
     <comment ref="B10" authorId="0" shapeId="0">
       <text>
-        <t>High FORMULA_DRIFT
+        <t>Critical RANGE_EXCLUSION
+Aggregation range appears to exclude adjacent data row
+Fix: Confirm whether Budget!B9 belongs in the aggregate, then extend the range if appropriate.
+High FORMULA_DRIFT
 Formula breaks neighboring pattern
-Fix: Compare this formula to adjacent formulas and restore the intended relative references.</t>
+Fix: If this cell is the same kind of line as its neighbors, restore their pattern. A total, net or summary line differs by design: compare it with the other totals instead.</t>
       </text>
     </comment>
     <comment ref="B13" authorId="0" shapeId="0">
@@ -177,7 +186,10 @@
     </comment>
     <comment ref="B14" authorId="0" shapeId="0">
       <text>
-        <t>High BROKEN_REFERENCE
+        <t>Critical LIVE_ERROR
+Cell contains live spreadsheet error
+Fix: Trace the formula precedent chain and resolve the underlying spreadsheet error.
+High BROKEN_REFERENCE
 Formula contains deleted reference
 Fix: Restore the deleted reference or rebuild the formula from intended source cells.</t>
       </text>

--- a/examples/demo_annotated.xlsx
+++ b/examples/demo_annotated.xlsx
@@ -198,21 +198,24 @@
       <text>
         <t>Medium DUPLICATE_KEY
 Duplicate key in lookup range
-Fix: Make the keys unique or confirm the lookup is meant to return the first match.</t>
+Fix: Make the keys unique or confirm the lookup is meant to return the first match.
+The same issue is in 1 other cell(s); fixing it here usually fixes them.</t>
       </text>
     </comment>
     <comment ref="A18" authorId="0" shapeId="0">
       <text>
-        <t>Medium WHITESPACE_KEY
+        <t>Medium DUPLICATE_KEY
+Same issue as Budget!A17, Budget!A18; see the comment there.
+Medium WHITESPACE_KEY
 Text has leading or trailing whitespace
-Fix: Trim the value if it is used as a lookup key or label.</t>
+Fix: Trim the values if they are used as lookup keys or labels.</t>
       </text>
     </comment>
     <comment ref="B20" authorId="0" shapeId="0">
       <text>
         <t>High NUMBERS_STORED_AS_TEXT
 Numeric-looking value stored as text
-Fix: Convert the value to a number or confirm it is intentionally text.</t>
+Fix: Convert the values to numbers or confirm they are intentionally text.</t>
       </text>
     </comment>
   </commentList>
